--- a/WorkBot/main/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Bakery_20260601.xlsx
+++ b/WorkBot/main/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Bakery_20260601.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -815,6 +815,27 @@
         <v>278.32</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Muffin Cup - 6"</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
